--- a/04_DESIGN_TABLES/DesignTable_6606.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6606.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,24 +714,71 @@
           <t>6606-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>6606-04-04-04-FG</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>7/16-20 x 7/16-20 x 7/16-20 (female JIC swivel all three ends)</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -737,6 +789,11 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>6606-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -783,24 +840,71 @@
           <t>6606-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.75</v>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>6606-08-08-08-FG</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3/4-16 x 3/4-16 x 3/4-16 (female JIC swivel all three ends)</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -811,6 +915,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>6606-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -820,24 +929,71 @@
           <t>6606-10-10-10-FG</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.875</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>6606-10-10-10-FG</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>7/8-14 x 7/8-14 x 7/8-14 (female JIC swivel all three ends)</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -848,6 +1004,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>6606-10-10-10-FG</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -894,24 +1055,71 @@
           <t>6606-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.3125</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>6606-16-16-16-FG</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1 5/16-12 x 1 5/16-12 x 1 5/16-12 (female JIC swivel all three ends)</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -922,6 +1130,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>6606-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6606.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6606.xlsx
@@ -803,24 +803,71 @@
           <t>6606-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>6606-06-06-06-FG</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>9/16-18 x 9/16-18 x 9/16-18 (female JIC swivel all three ends)</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_6606-06-06-06-FG.stp, every value equal to the catalog within 0.005); end details from the end library: M5_1@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M6 LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 1: axis crossing to the swivel nut face; own STEP: nut faces 1.25 / 1.255 / 1.25 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); M10_1@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M LGTH" = "0.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 1: axis crossing to the swivel nose tip; own STEP: nose tips 0.87 / 0.865 / 0.865 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)) - 0.005 under the catalog on two legs, the catalog value is kept (it prints this part; same manufacturer); C3_1HEX@HEX: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 1 swivel nut hex; own STEP: nut A/F 0.688 on all three (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); M5_2@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M6 LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 2: axis crossing to the swivel nut face; own STEP: nut faces 1.25 / 1.255 / 1.25 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); M10_2@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M LGTH" = "0.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 2: axis crossing to the swivel nose tip; own STEP: nose tips 0.87 / 0.865 / 0.865 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)) - 0.005 under the catalog on two legs, the catalog value is kept (it prints this part; same manufacturer); C3_2HEX@HEX: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 2 swivel nut hex; own STEP: nut A/F 0.688 on all three (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); M5_3@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M6 LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 3: axis crossing to the swivel nut face; own STEP: nut faces 1.25 / 1.255 / 1.25 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); M10_3@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "M LGTH" = "0.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 3: axis crossing to the swivel nose tip; own STEP: nose tips 0.87 / 0.865 / 0.865 (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)) - 0.005 under the catalog on two legs, the catalog value is kept (it prints this part; same manufacturer); C3_3HEX@HEX: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - leg 3 swivel nut hex; own STEP: nut A/F 0.688 on all three (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); Y@HEX: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: body flats 0.281 from the axis = 0.562 (tools/_out/wave2_shapes_20261008/PERLEGSW/evidence/step_survey.txt, this STEP); D1@BORE: Brennan TFA catalog p.58 table TFA-p058-t04 "6606-FG FJS-FJS-FJS TEE" row 6606-06-06-06-FG col "A1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 674.3, page verified True) [Brennan = yes 2026-10-18] - bore (A1 = A2 = A3 DRILL 0.297); own STEP: bores 0.297 on all three legs (C_ownstep/measure/6606-06-06-06-FG.txt + 66xx_branch_extra.txt (swiv._measure_leg, Brennan mode)); THDMAJ_B1@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B2@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B3@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 6606-6-6-6 (plain): M5 1.25 M10 0.88 C3 0.69 Y 0.63 D1 0.30 (Y differs: forged flats 0.562)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -831,6 +878,11 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>6606-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
